--- a/data_qr/2026-05-14.xlsx
+++ b/data_qr/2026-05-14.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BKP\Document BKP\Daily Reports\March 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Desktop\my_first_website\data_qr\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10188"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
   <si>
     <t>EthSwitch S.C.</t>
   </si>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>BANK</t>
   </si>
 </sst>
 </file>
@@ -148,7 +151,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -340,7 +343,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -626,20 +629,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="E2:I35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="5" max="5" width="19.44140625" customWidth="1"/>
-    <col min="6" max="6" width="18.109375" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="15.33203125" customWidth="1"/>
-    <col min="11" max="11" width="11.6640625"/>
-    <col min="13" max="13" width="11.6640625"/>
-    <col min="15" max="15" width="11.6640625"/>
+    <col min="10" max="10" width="15.28515625" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375"/>
+    <col min="13" max="13" width="11.7109375"/>
+    <col min="15" max="15" width="11.7109375"/>
   </cols>
   <sheetData>
-    <row r="2" spans="5:9" ht="15.6">
+    <row r="2" spans="5:9" ht="15.75">
       <c r="E2" s="14" t="s">
         <v>0</v>
       </c>
@@ -648,7 +651,7 @@
       <c r="H2" s="14"/>
       <c r="I2" s="14"/>
     </row>
-    <row r="3" spans="5:9" ht="15.6">
+    <row r="3" spans="5:9" ht="15.75">
       <c r="E3" s="14" t="s">
         <v>1</v>
       </c>
@@ -657,7 +660,7 @@
       <c r="H3" s="14"/>
       <c r="I3" s="14"/>
     </row>
-    <row r="4" spans="5:9" ht="15.6">
+    <row r="4" spans="5:9" ht="15.75">
       <c r="E4" s="15">
         <v>46156</v>
       </c>
@@ -666,7 +669,7 @@
       <c r="H4" s="15"/>
       <c r="I4" s="15"/>
     </row>
-    <row r="5" spans="5:9" ht="14.4" customHeight="1">
+    <row r="5" spans="5:9" ht="14.45" customHeight="1">
       <c r="E5" s="16" t="s">
         <v>2</v>
       </c>
@@ -675,8 +678,10 @@
       <c r="H5" s="16"/>
       <c r="I5" s="16"/>
     </row>
-    <row r="6" spans="5:9" ht="14.4" customHeight="1">
-      <c r="E6" s="17"/>
+    <row r="6" spans="5:9" ht="14.45" customHeight="1">
+      <c r="E6" s="17" t="s">
+        <v>36</v>
+      </c>
       <c r="F6" s="17" t="s">
         <v>3</v>
       </c>
@@ -686,7 +691,7 @@
       </c>
       <c r="I6" s="17"/>
     </row>
-    <row r="7" spans="5:9">
+    <row r="7" spans="5:9" ht="16.5">
       <c r="E7" s="17" t="s">
         <v>5</v>
       </c>
@@ -703,7 +708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="5:9">
+    <row r="8" spans="5:9" ht="16.5">
       <c r="E8" s="4" t="s">
         <v>8</v>
       </c>
@@ -720,7 +725,7 @@
         <v>82953</v>
       </c>
     </row>
-    <row r="9" spans="5:9">
+    <row r="9" spans="5:9" ht="16.5">
       <c r="E9" s="7" t="s">
         <v>9</v>
       </c>
@@ -737,7 +742,7 @@
         <v>6083509.5</v>
       </c>
     </row>
-    <row r="10" spans="5:9">
+    <row r="10" spans="5:9" ht="16.5">
       <c r="E10" s="7" t="s">
         <v>10</v>
       </c>
@@ -754,7 +759,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="11" spans="5:9">
+    <row r="11" spans="5:9" ht="16.5">
       <c r="E11" s="7" t="s">
         <v>11</v>
       </c>
@@ -771,7 +776,7 @@
         <v>19200</v>
       </c>
     </row>
-    <row r="12" spans="5:9">
+    <row r="12" spans="5:9" ht="16.5">
       <c r="E12" s="7" t="s">
         <v>12</v>
       </c>
@@ -788,7 +793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="5:9">
+    <row r="13" spans="5:9" ht="16.5">
       <c r="E13" s="7" t="s">
         <v>13</v>
       </c>
@@ -805,7 +810,7 @@
         <v>125908</v>
       </c>
     </row>
-    <row r="14" spans="5:9">
+    <row r="14" spans="5:9" ht="16.5">
       <c r="E14" s="7" t="s">
         <v>14</v>
       </c>
@@ -822,7 +827,7 @@
         <v>4016516.71</v>
       </c>
     </row>
-    <row r="15" spans="5:9">
+    <row r="15" spans="5:9" ht="16.5">
       <c r="E15" s="7" t="s">
         <v>15</v>
       </c>
@@ -839,7 +844,7 @@
         <v>33064.620000000003</v>
       </c>
     </row>
-    <row r="16" spans="5:9">
+    <row r="16" spans="5:9" ht="16.5">
       <c r="E16" s="7" t="s">
         <v>16</v>
       </c>
@@ -856,7 +861,7 @@
         <v>85000</v>
       </c>
     </row>
-    <row r="17" spans="5:9">
+    <row r="17" spans="5:9" ht="16.5">
       <c r="E17" s="7" t="s">
         <v>17</v>
       </c>
@@ -873,7 +878,7 @@
         <v>3984898.75</v>
       </c>
     </row>
-    <row r="18" spans="5:9">
+    <row r="18" spans="5:9" ht="16.5">
       <c r="E18" s="7" t="s">
         <v>18</v>
       </c>
@@ -890,7 +895,7 @@
         <v>17115.009999999998</v>
       </c>
     </row>
-    <row r="19" spans="5:9">
+    <row r="19" spans="5:9" ht="16.5">
       <c r="E19" s="7" t="s">
         <v>19</v>
       </c>
@@ -907,7 +912,7 @@
         <v>13042230.1</v>
       </c>
     </row>
-    <row r="20" spans="5:9">
+    <row r="20" spans="5:9" ht="16.5">
       <c r="E20" s="7" t="s">
         <v>20</v>
       </c>
@@ -924,7 +929,7 @@
         <v>4703553.08</v>
       </c>
     </row>
-    <row r="21" spans="5:9">
+    <row r="21" spans="5:9" ht="16.5">
       <c r="E21" s="7" t="s">
         <v>21</v>
       </c>
@@ -941,7 +946,7 @@
         <v>101311</v>
       </c>
     </row>
-    <row r="22" spans="5:9">
+    <row r="22" spans="5:9" ht="16.5">
       <c r="E22" s="7" t="s">
         <v>22</v>
       </c>
@@ -958,7 +963,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="23" spans="5:9">
+    <row r="23" spans="5:9" ht="16.5">
       <c r="E23" s="7" t="s">
         <v>23</v>
       </c>
@@ -975,7 +980,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="5:9">
+    <row r="24" spans="5:9" ht="16.5">
       <c r="E24" s="7" t="s">
         <v>24</v>
       </c>
@@ -992,7 +997,7 @@
         <v>3591178</v>
       </c>
     </row>
-    <row r="25" spans="5:9">
+    <row r="25" spans="5:9" ht="16.5">
       <c r="E25" s="7" t="s">
         <v>25</v>
       </c>
@@ -1009,7 +1014,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="5:9">
+    <row r="26" spans="5:9" ht="16.5">
       <c r="E26" s="7" t="s">
         <v>26</v>
       </c>
@@ -1026,7 +1031,7 @@
         <v>10377</v>
       </c>
     </row>
-    <row r="27" spans="5:9">
+    <row r="27" spans="5:9" ht="16.5">
       <c r="E27" s="7" t="s">
         <v>27</v>
       </c>
@@ -1043,7 +1048,7 @@
         <v>3750</v>
       </c>
     </row>
-    <row r="28" spans="5:9">
+    <row r="28" spans="5:9" ht="16.5">
       <c r="E28" s="7" t="s">
         <v>28</v>
       </c>
@@ -1060,7 +1065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="5:9">
+    <row r="29" spans="5:9" ht="16.5">
       <c r="E29" s="1" t="s">
         <v>29</v>
       </c>
@@ -1077,7 +1082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="5:9">
+    <row r="30" spans="5:9" ht="16.5">
       <c r="E30" s="1" t="s">
         <v>30</v>
       </c>
@@ -1094,7 +1099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="5:9">
+    <row r="31" spans="5:9" ht="16.5">
       <c r="E31" s="1" t="s">
         <v>31</v>
       </c>
@@ -1111,7 +1116,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="5:9">
+    <row r="32" spans="5:9" ht="16.5">
       <c r="E32" s="1" t="s">
         <v>32</v>
       </c>
@@ -1128,7 +1133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="5:9">
+    <row r="33" spans="5:9" ht="16.5">
       <c r="E33" s="7" t="s">
         <v>33</v>
       </c>
@@ -1145,7 +1150,7 @@
         <v>631125</v>
       </c>
     </row>
-    <row r="34" spans="5:9">
+    <row r="34" spans="5:9" ht="16.5">
       <c r="E34" s="7" t="s">
         <v>34</v>
       </c>
@@ -1162,7 +1167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="5:9">
+    <row r="35" spans="5:9" ht="16.5">
       <c r="E35" s="7" t="s">
         <v>35</v>
       </c>

--- a/data_qr/2026-05-14.xlsx
+++ b/data_qr/2026-05-14.xlsx
@@ -628,578 +628,578 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="E2:I35"/>
+  <dimension ref="B2:F35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="5" max="5" width="19.42578125" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" customWidth="1"/>
-    <col min="7" max="7" width="17.28515625" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="15.28515625" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375"/>
-    <col min="13" max="13" width="11.7109375"/>
-    <col min="15" max="15" width="11.7109375"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375"/>
+    <col min="10" max="10" width="11.7109375"/>
+    <col min="12" max="12" width="11.7109375"/>
   </cols>
   <sheetData>
-    <row r="2" spans="5:9" ht="15.75">
-      <c r="E2" s="14" t="s">
-        <v>0</v>
-      </c>
+    <row r="2" spans="2:6" ht="15.75">
+      <c r="B2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
       <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-    </row>
-    <row r="3" spans="5:9" ht="15.75">
-      <c r="E3" s="14" t="s">
+    </row>
+    <row r="3" spans="2:6" ht="15.75">
+      <c r="B3" s="14" t="s">
         <v>1</v>
       </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-    </row>
-    <row r="4" spans="5:9" ht="15.75">
-      <c r="E4" s="15">
+    </row>
+    <row r="4" spans="2:6" ht="15.75">
+      <c r="B4" s="15">
         <v>46156</v>
       </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
       <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-    </row>
-    <row r="5" spans="5:9" ht="14.45" customHeight="1">
-      <c r="E5" s="16" t="s">
+    </row>
+    <row r="5" spans="2:6" ht="14.45" customHeight="1">
+      <c r="B5" s="16" t="s">
         <v>2</v>
       </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
       <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-    </row>
-    <row r="6" spans="5:9" ht="14.45" customHeight="1">
+    </row>
+    <row r="6" spans="2:6" ht="14.45" customHeight="1">
+      <c r="B6" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="17"/>
       <c r="E6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="17"/>
+    </row>
+    <row r="7" spans="2:6" ht="16.5">
+      <c r="B7" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="16.5">
+      <c r="B8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="5">
+        <v>19</v>
+      </c>
+      <c r="D8" s="5">
+        <v>10005</v>
+      </c>
+      <c r="E8" s="6">
+        <v>13</v>
+      </c>
+      <c r="F8" s="6">
+        <v>82953</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="16.5">
+      <c r="B9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1239</v>
+      </c>
+      <c r="D9" s="5">
+        <v>12097142.75</v>
+      </c>
+      <c r="E9" s="6">
+        <v>367</v>
+      </c>
+      <c r="F9" s="6">
+        <v>6083509.5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="16.5">
+      <c r="B10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="8">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5">
+        <v>2821</v>
+      </c>
+      <c r="E10" s="6">
+        <v>4</v>
+      </c>
+      <c r="F10" s="6">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="16.5">
+      <c r="B11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="8">
+        <v>5</v>
+      </c>
+      <c r="D11" s="5">
+        <v>76</v>
+      </c>
+      <c r="E11" s="6">
+        <v>7</v>
+      </c>
+      <c r="F11" s="6">
+        <v>19200</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="16.5">
+      <c r="B12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="8">
+        <v>11</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2690</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="16.5">
+      <c r="B13" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="9">
+        <v>6</v>
+      </c>
+      <c r="D13" s="5">
+        <v>12361</v>
+      </c>
+      <c r="E13" s="5">
+        <v>12</v>
+      </c>
+      <c r="F13" s="6">
+        <v>125908</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="16.5">
+      <c r="B14" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="5">
+        <v>510</v>
+      </c>
+      <c r="D14" s="5">
+        <v>16782467.02</v>
+      </c>
+      <c r="E14" s="6">
+        <v>418</v>
+      </c>
+      <c r="F14" s="6">
+        <v>4016516.71</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" ht="16.5">
+      <c r="B15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="5">
+        <v>183</v>
+      </c>
+      <c r="D15" s="5">
+        <v>216916.24</v>
+      </c>
+      <c r="E15" s="6">
+        <v>9</v>
+      </c>
+      <c r="F15" s="6">
+        <v>33064.620000000003</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="16.5">
+      <c r="B16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="5">
+        <v>60</v>
+      </c>
+      <c r="D16" s="5">
+        <v>901399.38</v>
+      </c>
+      <c r="E16" s="6">
+        <v>2</v>
+      </c>
+      <c r="F16" s="6">
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="16.5">
+      <c r="B17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="5">
+        <v>380</v>
+      </c>
+      <c r="D17" s="5">
+        <v>4406304.5</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1809</v>
+      </c>
+      <c r="F17" s="6">
+        <v>3984898.75</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" ht="16.5">
+      <c r="B18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="5">
+        <v>34</v>
+      </c>
+      <c r="D18" s="5">
+        <v>101669</v>
+      </c>
+      <c r="E18" s="6">
+        <v>34</v>
+      </c>
+      <c r="F18" s="6">
+        <v>17115.009999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" ht="16.5">
+      <c r="B19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="5">
+        <v>60</v>
+      </c>
+      <c r="D19" s="5">
+        <v>118127</v>
+      </c>
+      <c r="E19" s="6">
+        <v>304</v>
+      </c>
+      <c r="F19" s="6">
+        <v>13042230.1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="16.5">
+      <c r="B20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="5">
+        <v>86</v>
+      </c>
+      <c r="D20" s="5">
+        <v>232202</v>
+      </c>
+      <c r="E20" s="6">
+        <v>159</v>
+      </c>
+      <c r="F20" s="6">
+        <v>4703553.08</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" ht="16.5">
+      <c r="B21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="5">
+        <v>5</v>
+      </c>
+      <c r="D21" s="5">
+        <v>1955</v>
+      </c>
+      <c r="E21" s="6">
+        <v>8</v>
+      </c>
+      <c r="F21" s="6">
+        <v>101311</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" ht="16.5">
+      <c r="B22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="5">
+        <v>1</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5</v>
+      </c>
+      <c r="E22" s="6">
+        <v>2</v>
+      </c>
+      <c r="F22" s="6">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" ht="16.5">
+      <c r="B23" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5">
+        <v>100</v>
+      </c>
+      <c r="E23" s="6">
+        <v>2</v>
+      </c>
+      <c r="F23" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" ht="16.5">
+      <c r="B24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="5">
+        <v>24</v>
+      </c>
+      <c r="D24" s="5">
+        <v>41203</v>
+      </c>
+      <c r="E24" s="6">
+        <v>89</v>
+      </c>
+      <c r="F24" s="6">
+        <v>3591178</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" ht="16.5">
+      <c r="B25" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="5">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5">
+        <v>0</v>
+      </c>
+      <c r="E25" s="6">
+        <v>2</v>
+      </c>
+      <c r="F25" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" ht="16.5">
+      <c r="B26" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="5">
+        <v>344</v>
+      </c>
+      <c r="D26" s="5">
+        <v>356257</v>
+      </c>
+      <c r="E26" s="6">
+        <v>28</v>
+      </c>
+      <c r="F26" s="6">
+        <v>10377</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" ht="16.5">
+      <c r="B27" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="10">
+        <v>6</v>
+      </c>
+      <c r="D27" s="5">
+        <v>105930</v>
+      </c>
+      <c r="E27" s="6">
+        <v>8</v>
+      </c>
+      <c r="F27" s="6">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" ht="16.5">
+      <c r="B28" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="10">
         <v>3</v>
       </c>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17" t="s">
+      <c r="D28" s="5">
+        <v>525</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0</v>
+      </c>
+      <c r="F28" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" ht="16.5">
+      <c r="B29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="10">
+        <v>3</v>
+      </c>
+      <c r="D29" s="5">
+        <v>10245</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" ht="16.5">
+      <c r="B30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="10">
+        <v>233</v>
+      </c>
+      <c r="D30" s="5">
+        <v>489810.88</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0</v>
+      </c>
+      <c r="F30" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" ht="16.5">
+      <c r="B31" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="11">
         <v>4</v>
       </c>
-      <c r="I6" s="17"/>
-    </row>
-    <row r="7" spans="5:9" ht="16.5">
-      <c r="E7" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="5:9" ht="16.5">
-      <c r="E8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="5">
-        <v>19</v>
-      </c>
-      <c r="G8" s="5">
-        <v>10005</v>
-      </c>
-      <c r="H8" s="6">
-        <v>13</v>
-      </c>
-      <c r="I8" s="6">
-        <v>82953</v>
-      </c>
-    </row>
-    <row r="9" spans="5:9" ht="16.5">
-      <c r="E9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="5">
-        <v>1239</v>
-      </c>
-      <c r="G9" s="5">
-        <v>12097142.75</v>
-      </c>
-      <c r="H9" s="6">
-        <v>367</v>
-      </c>
-      <c r="I9" s="6">
-        <v>6083509.5</v>
-      </c>
-    </row>
-    <row r="10" spans="5:9" ht="16.5">
-      <c r="E10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="8">
-        <v>2</v>
-      </c>
-      <c r="G10" s="5">
-        <v>2821</v>
-      </c>
-      <c r="H10" s="6">
-        <v>4</v>
-      </c>
-      <c r="I10" s="6">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="11" spans="5:9" ht="16.5">
-      <c r="E11" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="8">
-        <v>5</v>
-      </c>
-      <c r="G11" s="5">
-        <v>76</v>
-      </c>
-      <c r="H11" s="6">
-        <v>7</v>
-      </c>
-      <c r="I11" s="6">
-        <v>19200</v>
-      </c>
-    </row>
-    <row r="12" spans="5:9" ht="16.5">
-      <c r="E12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="8">
-        <v>11</v>
-      </c>
-      <c r="G12" s="5">
-        <v>2690</v>
-      </c>
-      <c r="H12" s="6">
-        <v>0</v>
-      </c>
-      <c r="I12" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="5:9" ht="16.5">
-      <c r="E13" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="9">
-        <v>6</v>
-      </c>
-      <c r="G13" s="5">
-        <v>12361</v>
-      </c>
-      <c r="H13" s="5">
-        <v>12</v>
-      </c>
-      <c r="I13" s="6">
-        <v>125908</v>
-      </c>
-    </row>
-    <row r="14" spans="5:9" ht="16.5">
-      <c r="E14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="5">
-        <v>510</v>
-      </c>
-      <c r="G14" s="5">
-        <v>16782467.02</v>
-      </c>
-      <c r="H14" s="6">
-        <v>418</v>
-      </c>
-      <c r="I14" s="6">
-        <v>4016516.71</v>
-      </c>
-    </row>
-    <row r="15" spans="5:9" ht="16.5">
-      <c r="E15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="5">
-        <v>183</v>
-      </c>
-      <c r="G15" s="5">
-        <v>216916.24</v>
-      </c>
-      <c r="H15" s="6">
-        <v>9</v>
-      </c>
-      <c r="I15" s="6">
-        <v>33064.620000000003</v>
-      </c>
-    </row>
-    <row r="16" spans="5:9" ht="16.5">
-      <c r="E16" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="5">
-        <v>60</v>
-      </c>
-      <c r="G16" s="5">
-        <v>901399.38</v>
-      </c>
-      <c r="H16" s="6">
-        <v>2</v>
-      </c>
-      <c r="I16" s="6">
-        <v>85000</v>
-      </c>
-    </row>
-    <row r="17" spans="5:9" ht="16.5">
-      <c r="E17" s="7" t="s">
+      <c r="D31" s="5">
+        <v>1094</v>
+      </c>
+      <c r="E31" s="6">
+        <v>1</v>
+      </c>
+      <c r="F31" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" ht="16.5">
+      <c r="B32" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="12">
         <v>17</v>
       </c>
-      <c r="F17" s="5">
-        <v>380</v>
-      </c>
-      <c r="G17" s="5">
-        <v>4406304.5</v>
-      </c>
-      <c r="H17" s="6">
-        <v>1809</v>
-      </c>
-      <c r="I17" s="6">
-        <v>3984898.75</v>
-      </c>
-    </row>
-    <row r="18" spans="5:9" ht="16.5">
-      <c r="E18" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="5">
+      <c r="D32" s="6">
+        <v>1972</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0</v>
+      </c>
+      <c r="F32" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" ht="16.5">
+      <c r="B33" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0</v>
+      </c>
+      <c r="D33" s="6">
+        <v>0</v>
+      </c>
+      <c r="E33" s="6">
+        <v>27</v>
+      </c>
+      <c r="F33" s="6">
+        <v>631125</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" ht="16.5">
+      <c r="B34" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G18" s="5">
-        <v>101669</v>
-      </c>
-      <c r="H18" s="6">
-        <v>34</v>
-      </c>
-      <c r="I18" s="6">
-        <v>17115.009999999998</v>
-      </c>
-    </row>
-    <row r="19" spans="5:9" ht="16.5">
-      <c r="E19" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" s="5">
-        <v>60</v>
-      </c>
-      <c r="G19" s="5">
-        <v>118127</v>
-      </c>
-      <c r="H19" s="6">
-        <v>304</v>
-      </c>
-      <c r="I19" s="6">
-        <v>13042230.1</v>
-      </c>
-    </row>
-    <row r="20" spans="5:9" ht="16.5">
-      <c r="E20" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F20" s="5">
-        <v>86</v>
-      </c>
-      <c r="G20" s="5">
-        <v>232202</v>
-      </c>
-      <c r="H20" s="6">
-        <v>159</v>
-      </c>
-      <c r="I20" s="6">
-        <v>4703553.08</v>
-      </c>
-    </row>
-    <row r="21" spans="5:9" ht="16.5">
-      <c r="E21" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F21" s="5">
-        <v>5</v>
-      </c>
-      <c r="G21" s="5">
-        <v>1955</v>
-      </c>
-      <c r="H21" s="6">
-        <v>8</v>
-      </c>
-      <c r="I21" s="6">
-        <v>101311</v>
-      </c>
-    </row>
-    <row r="22" spans="5:9" ht="16.5">
-      <c r="E22" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="5">
-        <v>1</v>
-      </c>
-      <c r="G22" s="5">
-        <v>5</v>
-      </c>
-      <c r="H22" s="6">
-        <v>2</v>
-      </c>
-      <c r="I22" s="6">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="23" spans="5:9" ht="16.5">
-      <c r="E23" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" s="5">
-        <v>1</v>
-      </c>
-      <c r="G23" s="5">
-        <v>100</v>
-      </c>
-      <c r="H23" s="6">
-        <v>2</v>
-      </c>
-      <c r="I23" s="6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="5:9" ht="16.5">
-      <c r="E24" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F24" s="5">
-        <v>24</v>
-      </c>
-      <c r="G24" s="5">
-        <v>41203</v>
-      </c>
-      <c r="H24" s="6">
-        <v>89</v>
-      </c>
-      <c r="I24" s="6">
-        <v>3591178</v>
-      </c>
-    </row>
-    <row r="25" spans="5:9" ht="16.5">
-      <c r="E25" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="5">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6">
-        <v>2</v>
-      </c>
-      <c r="I25" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="5:9" ht="16.5">
-      <c r="E26" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26" s="5">
-        <v>344</v>
-      </c>
-      <c r="G26" s="5">
-        <v>356257</v>
-      </c>
-      <c r="H26" s="6">
-        <v>28</v>
-      </c>
-      <c r="I26" s="6">
-        <v>10377</v>
-      </c>
-    </row>
-    <row r="27" spans="5:9" ht="16.5">
-      <c r="E27" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F27" s="10">
-        <v>6</v>
-      </c>
-      <c r="G27" s="5">
-        <v>105930</v>
-      </c>
-      <c r="H27" s="6">
-        <v>8</v>
-      </c>
-      <c r="I27" s="6">
-        <v>3750</v>
-      </c>
-    </row>
-    <row r="28" spans="5:9" ht="16.5">
-      <c r="E28" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F28" s="10">
-        <v>3</v>
-      </c>
-      <c r="G28" s="5">
-        <v>525</v>
-      </c>
-      <c r="H28" s="6">
-        <v>0</v>
-      </c>
-      <c r="I28" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="5:9" ht="16.5">
-      <c r="E29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F29" s="10">
-        <v>3</v>
-      </c>
-      <c r="G29" s="5">
-        <v>10245</v>
-      </c>
-      <c r="H29" s="6">
-        <v>0</v>
-      </c>
-      <c r="I29" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="5:9" ht="16.5">
-      <c r="E30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F30" s="10">
-        <v>233</v>
-      </c>
-      <c r="G30" s="5">
-        <v>489810.88</v>
-      </c>
-      <c r="H30" s="6">
-        <v>0</v>
-      </c>
-      <c r="I30" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="5:9" ht="16.5">
-      <c r="E31" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F31" s="11">
-        <v>4</v>
-      </c>
-      <c r="G31" s="5">
-        <v>1094</v>
-      </c>
-      <c r="H31" s="6">
-        <v>1</v>
-      </c>
-      <c r="I31" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="5:9" ht="16.5">
-      <c r="E32" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F32" s="12">
-        <v>17</v>
-      </c>
-      <c r="G32" s="6">
-        <v>1972</v>
-      </c>
-      <c r="H32" s="6">
-        <v>0</v>
-      </c>
-      <c r="I32" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="5:9" ht="16.5">
-      <c r="E33" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F33" s="6">
-        <v>0</v>
-      </c>
-      <c r="G33" s="6">
-        <v>0</v>
-      </c>
-      <c r="H33" s="6">
-        <v>27</v>
-      </c>
-      <c r="I33" s="6">
-        <v>631125</v>
-      </c>
-    </row>
-    <row r="34" spans="5:9" ht="16.5">
-      <c r="E34" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F34" s="9">
+      <c r="C34" s="9">
         <v>69</v>
       </c>
-      <c r="G34" s="5">
+      <c r="D34" s="5">
         <v>639078</v>
       </c>
-      <c r="H34" s="6">
-        <v>0</v>
-      </c>
-      <c r="I34" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="5:9" ht="16.5">
-      <c r="E35" s="7" t="s">
+      <c r="E34" s="6">
+        <v>0</v>
+      </c>
+      <c r="F34" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" ht="16.5">
+      <c r="B35" s="7" t="s">
         <v>35</v>
+      </c>
+      <c r="C35" s="13">
+        <f>SUM(C8:C34)</f>
+        <v>3305</v>
+      </c>
+      <c r="D35" s="13">
+        <f>SUM(D8:D34)</f>
+        <v>36532355.770000003</v>
+      </c>
+      <c r="E35" s="13">
+        <f>SUM(E8:E34)</f>
+        <v>3305</v>
       </c>
       <c r="F35" s="13">
         <f>SUM(F8:F34)</f>
-        <v>3305</v>
-      </c>
-      <c r="G35" s="13">
-        <f>SUM(G8:G34)</f>
-        <v>36532355.770000003</v>
-      </c>
-      <c r="H35" s="13">
-        <f>SUM(H8:H34)</f>
-        <v>3305</v>
-      </c>
-      <c r="I35" s="13">
-        <f>SUM(I8:I34)</f>
-        <v>36532355.770000003</v>
+        <v>36532355.769999996</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="K8:O29">
-    <sortCondition ref="K8"/>
+  <sortState ref="H8:L29">
+    <sortCondition ref="H8"/>
   </sortState>
   <mergeCells count="7">
-    <mergeCell ref="E2:I2"/>
-    <mergeCell ref="E3:I3"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="E5:I5"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="B6:B7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
